--- a/data/trans_orig/P13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P13-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2007</t>
+          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>642267</t>
+          <t>646259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>706224</t>
+          <t>706414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>699631</t>
+          <t>700837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>772521</t>
+          <t>769657</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1365037</t>
+          <t>1360810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1461983</t>
+          <t>1454877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136660</t>
+          <t>135616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182808</t>
+          <t>186071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>219023</t>
+          <t>218783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273506</t>
+          <t>275631</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>367133</t>
+          <t>368412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>440788</t>
+          <t>444264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120762</t>
+          <t>120868</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163294</t>
+          <t>164765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>213548</t>
+          <t>212552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>272204</t>
+          <t>268016</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>346744</t>
+          <t>348496</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>419282</t>
+          <t>418195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38168</t>
+          <t>39878</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46009</t>
+          <t>44554</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76780</t>
+          <t>75842</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67334</t>
+          <t>68496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103313</t>
+          <t>104051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41169</t>
+          <t>42313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25277</t>
+          <t>25705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>50296</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49750</t>
+          <t>49363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82732</t>
+          <t>82896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1409841</t>
+          <t>1410902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1470918</t>
+          <t>1469160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1199867</t>
+          <t>1195553</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1265800</t>
+          <t>1264612</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2629426</t>
+          <t>2629952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2719798</t>
+          <t>2717299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,82%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117593</t>
+          <t>114628</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161670</t>
+          <t>159430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143435</t>
+          <t>143323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>194890</t>
+          <t>195612</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>272515</t>
+          <t>275537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>336682</t>
+          <t>342932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59567</t>
+          <t>59813</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93519</t>
+          <t>93467</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115483</t>
+          <t>116615</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161908</t>
+          <t>162189</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>185154</t>
+          <t>183950</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>240429</t>
+          <t>242728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>16088</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34504</t>
+          <t>35596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17031</t>
+          <t>17771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37764</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36703</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65695</t>
+          <t>65809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>25739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>16759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36130</t>
+          <t>36118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28762</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55421</t>
+          <t>55367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>455349</t>
+          <t>453962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>488752</t>
+          <t>487971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>355908</t>
+          <t>354479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>392409</t>
+          <t>391466</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>822849</t>
+          <t>820520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>872379</t>
+          <t>874758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,11%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>30612</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54748</t>
+          <t>57048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33099</t>
+          <t>32942</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58210</t>
+          <t>60131</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69696</t>
+          <t>69952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107713</t>
+          <t>107071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18026</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>36735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27750</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53190</t>
+          <t>51360</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49978</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79787</t>
+          <t>81181</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20557</t>
+          <t>20505</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>23944</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2539020</t>
+          <t>2540627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2633213</t>
+          <t>2635958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2290260</t>
+          <t>2283746</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2396815</t>
+          <t>2395384</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4857636</t>
+          <t>4849839</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5015093</t>
+          <t>5000034</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>304612</t>
+          <t>306729</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>377710</t>
+          <t>378425</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>423187</t>
+          <t>417314</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>502339</t>
+          <t>499032</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>742152</t>
+          <t>747885</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>849983</t>
+          <t>852255</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>214391</t>
+          <t>213165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>271492</t>
+          <t>271724</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>377213</t>
+          <t>379230</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>459638</t>
+          <t>454774</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>607867</t>
+          <t>609731</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>704473</t>
+          <t>709470</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38991</t>
+          <t>40694</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>69506</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>78724</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117139</t>
+          <t>118784</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125915</t>
+          <t>127698</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>175544</t>
+          <t>173915</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38490</t>
+          <t>39909</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67311</t>
+          <t>70377</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50543</t>
+          <t>51183</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>98354</t>
+          <t>97861</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>145389</t>
+          <t>142815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2012</t>
+          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>543203</t>
+          <t>539919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>607283</t>
+          <t>602389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>573198</t>
+          <t>574035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>648641</t>
+          <t>648604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1126889</t>
+          <t>1130646</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1227161</t>
+          <t>1229051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160128</t>
+          <t>161707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>211828</t>
+          <t>212430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236365</t>
+          <t>233180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297280</t>
+          <t>291997</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>410014</t>
+          <t>413079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>493087</t>
+          <t>489053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123611</t>
+          <t>121644</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>167756</t>
+          <t>168045</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>231663</t>
+          <t>231876</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>290791</t>
+          <t>290512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>371205</t>
+          <t>369744</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>446977</t>
+          <t>444415</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28340</t>
+          <t>28971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55260</t>
+          <t>54808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98349</t>
+          <t>99891</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139917</t>
+          <t>140747</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135212</t>
+          <t>135974</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182998</t>
+          <t>184281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44347</t>
+          <t>44105</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65955</t>
+          <t>64745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102025</t>
+          <t>101032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91009</t>
+          <t>94881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136857</t>
+          <t>137890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1546331</t>
+          <t>1546211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1618438</t>
+          <t>1614967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1224864</t>
+          <t>1224161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1305255</t>
+          <t>1299070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2790113</t>
+          <t>2789843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2901684</t>
+          <t>2894641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,86%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152247</t>
+          <t>154355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205843</t>
+          <t>205997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>183645</t>
+          <t>185199</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239706</t>
+          <t>238917</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348563</t>
+          <t>355265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>427368</t>
+          <t>431179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101327</t>
+          <t>100582</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146066</t>
+          <t>147013</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>149254</t>
+          <t>148992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>201420</t>
+          <t>200273</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>264233</t>
+          <t>262999</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>336492</t>
+          <t>334325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42377</t>
+          <t>42919</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75287</t>
+          <t>74999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59981</t>
+          <t>57947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93390</t>
+          <t>93800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111423</t>
+          <t>111330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158171</t>
+          <t>157808</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28481</t>
+          <t>28891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25108</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>49796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>41209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71707</t>
+          <t>70828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>392329</t>
+          <t>392050</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>427428</t>
+          <t>426543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>351469</t>
+          <t>348567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>386195</t>
+          <t>385564</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>755366</t>
+          <t>754288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>804017</t>
+          <t>803660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>25487</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>49039</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34274</t>
+          <t>35664</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>62149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63916</t>
+          <t>64636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>100759</t>
+          <t>102990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33536</t>
+          <t>32967</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38299</t>
+          <t>39407</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33923</t>
+          <t>33998</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65474</t>
+          <t>63098</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20981</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20986</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>15121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35368</t>
+          <t>36555</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2511439</t>
+          <t>2513759</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2620305</t>
+          <t>2619512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2178924</t>
+          <t>2181212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2295051</t>
+          <t>2303258</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4730602</t>
+          <t>4723870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4890763</t>
+          <t>4884065</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,09%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>362510</t>
+          <t>362759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>438322</t>
+          <t>440781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>477654</t>
+          <t>478962</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>565661</t>
+          <t>563811</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>862349</t>
+          <t>859464</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>978598</t>
+          <t>978193</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>255930</t>
+          <t>256361</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>321352</t>
+          <t>325985</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423308</t>
+          <t>421600</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>506364</t>
+          <t>501412</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>696572</t>
+          <t>701547</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>802052</t>
+          <t>803945</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>87544</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132720</t>
+          <t>130679</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177654</t>
+          <t>178056</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>232781</t>
+          <t>234754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>279995</t>
+          <t>280015</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>348511</t>
+          <t>350146</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>38012</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68004</t>
+          <t>67451</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>98976</t>
+          <t>102032</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146123</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>149375</t>
+          <t>149082</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>201655</t>
+          <t>202858</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2016</t>
+          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2016 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>482649</t>
+          <t>483730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>531536</t>
+          <t>534075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>500894</t>
+          <t>502803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>565946</t>
+          <t>567026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1000517</t>
+          <t>1001241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1085855</t>
+          <t>1083584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,03%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88210</t>
+          <t>86977</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125301</t>
+          <t>124251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137905</t>
+          <t>137914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186354</t>
+          <t>185537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>233454</t>
+          <t>235159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>295605</t>
+          <t>297806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78064</t>
+          <t>78887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115177</t>
+          <t>115981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164887</t>
+          <t>164012</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>214252</t>
+          <t>216638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256193</t>
+          <t>254520</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>319749</t>
+          <t>318952</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>38665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55809</t>
+          <t>56457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89103</t>
+          <t>92134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81376</t>
+          <t>79893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119122</t>
+          <t>121649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27803</t>
+          <t>27630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23066</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48527</t>
+          <t>48364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>38313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66487</t>
+          <t>68866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1647537</t>
+          <t>1646642</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1722840</t>
+          <t>1719448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1437346</t>
+          <t>1438642</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1516398</t>
+          <t>1515428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3105886</t>
+          <t>3112331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3220902</t>
+          <t>3218821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,23%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>218881</t>
+          <t>217648</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278625</t>
+          <t>279583</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243193</t>
+          <t>245806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307038</t>
+          <t>309570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>480764</t>
+          <t>482383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>564232</t>
+          <t>566371</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67442</t>
+          <t>66436</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102661</t>
+          <t>102928</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>139786</t>
+          <t>140620</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>189075</t>
+          <t>190097</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>216055</t>
+          <t>215678</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>282436</t>
+          <t>279460</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19498</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42996</t>
+          <t>42959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32550</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60927</t>
+          <t>59599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>55915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91554</t>
+          <t>93968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43495</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39162</t>
+          <t>38742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40970</t>
+          <t>41221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73145</t>
+          <t>72530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>431669</t>
+          <t>430475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>470179</t>
+          <t>468469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>424390</t>
+          <t>423633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>463276</t>
+          <t>463013</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>869673</t>
+          <t>868699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>922834</t>
+          <t>924402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47809</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80133</t>
+          <t>80305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38779</t>
+          <t>38618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66290</t>
+          <t>65764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94035</t>
+          <t>95545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136568</t>
+          <t>139048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31655</t>
+          <t>32023</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21544</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>44918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38387</t>
+          <t>37827</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68554</t>
+          <t>66844</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>23376</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15147</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36726</t>
+          <t>37320</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2590787</t>
+          <t>2590882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2692338</t>
+          <t>2687556</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2392629</t>
+          <t>2398212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2508052</t>
+          <t>2513657</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5023327</t>
+          <t>5025609</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5183753</t>
+          <t>5171193</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,9%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>379950</t>
+          <t>380073</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>458627</t>
+          <t>457986</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>447140</t>
+          <t>447164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>529783</t>
+          <t>529044</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>843496</t>
+          <t>850780</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>963315</t>
+          <t>963362</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174129</t>
+          <t>174999</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>232803</t>
+          <t>229589</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>347197</t>
+          <t>347291</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425543</t>
+          <t>425600</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>537496</t>
+          <t>538648</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>635474</t>
+          <t>633237</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52883</t>
+          <t>52889</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87804</t>
+          <t>85811</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106700</t>
+          <t>106999</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>154068</t>
+          <t>151760</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>170023</t>
+          <t>171883</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>226765</t>
+          <t>228574</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36046</t>
+          <t>36910</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>65236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48963</t>
+          <t>49727</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83715</t>
+          <t>85514</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92934</t>
+          <t>92290</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138207</t>
+          <t>137391</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2023</t>
+          <t>Población según frecuencia de dificultad de sus actividades por problemas (fìsicos o emocionales) en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>298571</t>
+          <t>300338</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>342078</t>
+          <t>341620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>340903</t>
+          <t>343714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>383308</t>
+          <t>387795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>655773</t>
+          <t>655976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>714566</t>
+          <t>715479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,49%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47087</t>
+          <t>47766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75415</t>
+          <t>73741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94195</t>
+          <t>93837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122205</t>
+          <t>122660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148694</t>
+          <t>149228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186844</t>
+          <t>185722</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58009</t>
+          <t>56626</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86998</t>
+          <t>84370</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131672</t>
+          <t>130708</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167406</t>
+          <t>168911</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>197438</t>
+          <t>195171</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>243838</t>
+          <t>241429</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>30012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51823</t>
+          <t>51100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61351</t>
+          <t>60992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85200</t>
+          <t>84711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95756</t>
+          <t>94183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128265</t>
+          <t>127965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51126</t>
+          <t>51486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73835</t>
+          <t>73218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71140</t>
+          <t>72102</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100090</t>
+          <t>99822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1813458</t>
+          <t>1815456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1997439</t>
+          <t>1997995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1091881</t>
+          <t>1152756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1696709</t>
+          <t>1698362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2898059</t>
+          <t>2874107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3598733</t>
+          <t>3613054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125655</t>
+          <t>124841</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214217</t>
+          <t>214307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>200187</t>
+          <t>200629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>929261</t>
+          <t>830885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>372753</t>
+          <t>366808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1153159</t>
+          <t>1189156</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104598</t>
+          <t>106893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>185828</t>
+          <t>184714</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164314</t>
+          <t>164605</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>258919</t>
+          <t>261859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>300595</t>
+          <t>296539</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>426843</t>
+          <t>425739</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32232</t>
+          <t>33256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63777</t>
+          <t>65300</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43869</t>
+          <t>43998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79364</t>
+          <t>79345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84768</t>
+          <t>89141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133648</t>
+          <t>134052</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19266</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45609</t>
+          <t>44430</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>23763</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45293</t>
+          <t>46868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49396</t>
+          <t>48176</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84720</t>
+          <t>83688</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>514709</t>
+          <t>515261</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>556893</t>
+          <t>556644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>496960</t>
+          <t>495997</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>533930</t>
+          <t>532418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1029156</t>
+          <t>1027058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1083015</t>
+          <t>1080035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29711</t>
+          <t>28845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55853</t>
+          <t>55749</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55931</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82324</t>
+          <t>83996</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91554</t>
+          <t>91493</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130437</t>
+          <t>128664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29975</t>
+          <t>31019</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59506</t>
+          <t>58178</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45533</t>
+          <t>45185</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70249</t>
+          <t>69634</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83500</t>
+          <t>81451</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120939</t>
+          <t>121102</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29913</t>
+          <t>29401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>25449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>13811</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34344</t>
+          <t>35461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2662897</t>
+          <t>2662891</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2895185</t>
+          <t>2904601</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1986319</t>
+          <t>1958851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2569759</t>
+          <t>2568323</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4627659</t>
+          <t>4652273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5341578</t>
+          <t>5352494</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217112</t>
+          <t>216770</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>316259</t>
+          <t>316653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>377456</t>
+          <t>374026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1109753</t>
+          <t>1134743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>648657</t>
+          <t>640042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1528737</t>
+          <t>1476292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>208298</t>
+          <t>202235</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>303513</t>
+          <t>304660</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>356496</t>
+          <t>356255</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>471916</t>
+          <t>474055</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>597376</t>
+          <t>585932</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>755674</t>
+          <t>754070</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73120</t>
+          <t>73912</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119115</t>
+          <t>118778</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119928</t>
+          <t>118982</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168012</t>
+          <t>166909</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>206317</t>
+          <t>208134</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>273557</t>
+          <t>276181</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50834</t>
+          <t>51429</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>87678</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>84681</t>
+          <t>82677</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>122378</t>
+          <t>123093</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>147167</t>
+          <t>146929</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>202998</t>
+          <t>199889</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P13-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>646259</t>
+          <t>645269</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>706414</t>
+          <t>706625</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>700837</t>
+          <t>699958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>769657</t>
+          <t>771474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1360810</t>
+          <t>1364660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1454877</t>
+          <t>1457063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135616</t>
+          <t>138762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186071</t>
+          <t>185459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218783</t>
+          <t>219676</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275631</t>
+          <t>275198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368412</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>444264</t>
+          <t>446816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120868</t>
+          <t>118917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164765</t>
+          <t>162970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>212552</t>
+          <t>213634</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>268016</t>
+          <t>268871</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>348496</t>
+          <t>345292</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>418195</t>
+          <t>417506</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16932</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39878</t>
+          <t>37641</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44554</t>
+          <t>44123</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75842</t>
+          <t>75242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68496</t>
+          <t>67761</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104051</t>
+          <t>103667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>19877</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42313</t>
+          <t>42021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25705</t>
+          <t>23322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50296</t>
+          <t>48793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49363</t>
+          <t>49719</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82896</t>
+          <t>81174</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1410902</t>
+          <t>1413218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1469160</t>
+          <t>1469934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1195553</t>
+          <t>1196142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1264612</t>
+          <t>1263661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2629952</t>
+          <t>2625488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2717299</t>
+          <t>2713706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114628</t>
+          <t>117004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159430</t>
+          <t>163252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143323</t>
+          <t>143847</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195612</t>
+          <t>192130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275537</t>
+          <t>275080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>342932</t>
+          <t>340931</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59813</t>
+          <t>58771</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93467</t>
+          <t>91737</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>116615</t>
+          <t>112855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162189</t>
+          <t>160135</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>183950</t>
+          <t>183909</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>242728</t>
+          <t>239907</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>15351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35596</t>
+          <t>35814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17771</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>39126</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>36964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65809</t>
+          <t>64819</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25739</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16759</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36118</t>
+          <t>37169</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>29475</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>55497</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>453962</t>
+          <t>455342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>487971</t>
+          <t>487422</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>354479</t>
+          <t>357025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>391466</t>
+          <t>392347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>820520</t>
+          <t>817571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>874758</t>
+          <t>871879</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30612</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57048</t>
+          <t>59809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>32007</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60131</t>
+          <t>59290</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69952</t>
+          <t>69528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107071</t>
+          <t>105890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27778</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51360</t>
+          <t>51689</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50933</t>
+          <t>50528</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81181</t>
+          <t>81357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>20189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24571</t>
+          <t>24873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15439</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23944</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2540627</t>
+          <t>2542975</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2635958</t>
+          <t>2633610</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2283746</t>
+          <t>2291462</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2395384</t>
+          <t>2397494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4849839</t>
+          <t>4857284</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5000034</t>
+          <t>5005205</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>306729</t>
+          <t>304799</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>378425</t>
+          <t>377540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>417314</t>
+          <t>416053</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>499032</t>
+          <t>497395</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>747885</t>
+          <t>745396</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>852255</t>
+          <t>853345</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>213165</t>
+          <t>214118</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>271724</t>
+          <t>274003</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>379230</t>
+          <t>376096</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>454774</t>
+          <t>451334</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>609731</t>
+          <t>608345</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>709470</t>
+          <t>705799</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40694</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69506</t>
+          <t>68329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78724</t>
+          <t>78785</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118784</t>
+          <t>117156</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>127698</t>
+          <t>126753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>173915</t>
+          <t>175340</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39909</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70377</t>
+          <t>68449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51183</t>
+          <t>52756</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84447</t>
+          <t>84286</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,47 +3281,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>118771</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>100626</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>144150</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>118771</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>97861</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>142815</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>539919</t>
+          <t>541837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>602389</t>
+          <t>603926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>574035</t>
+          <t>569622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>648604</t>
+          <t>645838</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1130646</t>
+          <t>1134954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1229051</t>
+          <t>1231662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,31%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161707</t>
+          <t>161908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>212430</t>
+          <t>212551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233180</t>
+          <t>235084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291997</t>
+          <t>294290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>413079</t>
+          <t>409838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>489053</t>
+          <t>490419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121644</t>
+          <t>123531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>168045</t>
+          <t>167523</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>231876</t>
+          <t>234060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>290512</t>
+          <t>291624</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>369744</t>
+          <t>368290</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>444415</t>
+          <t>444426</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28971</t>
+          <t>28425</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54808</t>
+          <t>54045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99891</t>
+          <t>100156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140747</t>
+          <t>141570</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135974</t>
+          <t>136041</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184281</t>
+          <t>185684</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>20041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44105</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64745</t>
+          <t>64532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101032</t>
+          <t>101676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94881</t>
+          <t>92508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>137890</t>
+          <t>134762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1546211</t>
+          <t>1546316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1614967</t>
+          <t>1621259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1224161</t>
+          <t>1225645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1299070</t>
+          <t>1299111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2789843</t>
+          <t>2791536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2894641</t>
+          <t>2898046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>154355</t>
+          <t>153006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205997</t>
+          <t>204463</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>185199</t>
+          <t>181757</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>238917</t>
+          <t>238741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355265</t>
+          <t>352383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>431179</t>
+          <t>426950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100582</t>
+          <t>103634</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147013</t>
+          <t>148510</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148992</t>
+          <t>147868</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>200273</t>
+          <t>198953</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>262999</t>
+          <t>265699</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>334325</t>
+          <t>330021</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42919</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74999</t>
+          <t>71112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57947</t>
+          <t>57662</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93800</t>
+          <t>92557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111330</t>
+          <t>110475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157808</t>
+          <t>159202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28891</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,74 +4841,74 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24233</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>50324</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>54825</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>41399</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>71565</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>1,47%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>24157</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>49796</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>54825</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>41209</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>70828</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>392050</t>
+          <t>392314</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>426543</t>
+          <t>428057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348567</t>
+          <t>350783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>385564</t>
+          <t>386257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>754288</t>
+          <t>754250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>803660</t>
+          <t>804866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>24519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49039</t>
+          <t>50062</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>34793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62149</t>
+          <t>61883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64636</t>
+          <t>65009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102990</t>
+          <t>102201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32967</t>
+          <t>34481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>17758</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39407</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>34847</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63098</t>
+          <t>65655</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36555</t>
+          <t>34767</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2513759</t>
+          <t>2510255</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2619512</t>
+          <t>2617501</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2181212</t>
+          <t>2183400</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2303258</t>
+          <t>2302284</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4723870</t>
+          <t>4729102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4884065</t>
+          <t>4892434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,21%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>362759</t>
+          <t>362174</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>440781</t>
+          <t>439234</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>478962</t>
+          <t>478270</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>563811</t>
+          <t>567519</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>859464</t>
+          <t>864797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>978193</t>
+          <t>981548</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>256361</t>
+          <t>259038</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>325985</t>
+          <t>327588</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>421600</t>
+          <t>422237</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>501412</t>
+          <t>505420</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>701547</t>
+          <t>697238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>803945</t>
+          <t>804499</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87544</t>
+          <t>89311</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>130679</t>
+          <t>132997</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>178056</t>
+          <t>179327</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>234754</t>
+          <t>236569</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,47 +6127,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>314020</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>279940</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>349140</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>5,01%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>314020</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>280015</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>350146</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38012</t>
+          <t>37662</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67451</t>
+          <t>68459</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102032</t>
+          <t>102428</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>147134</t>
+          <t>148357</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>149082</t>
+          <t>146741</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>202858</t>
+          <t>203244</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>483730</t>
+          <t>479533</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>534075</t>
+          <t>530486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>502803</t>
+          <t>504176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>567026</t>
+          <t>571001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1001241</t>
+          <t>1000254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1083584</t>
+          <t>1086874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86977</t>
+          <t>88917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124251</t>
+          <t>125019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137914</t>
+          <t>137386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185537</t>
+          <t>185945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235159</t>
+          <t>237156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>297806</t>
+          <t>300450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78887</t>
+          <t>80299</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115981</t>
+          <t>117735</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164012</t>
+          <t>164791</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>216638</t>
+          <t>215166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>254520</t>
+          <t>253178</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>318952</t>
+          <t>319276</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18810</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38665</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56457</t>
+          <t>56303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92134</t>
+          <t>89302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79893</t>
+          <t>81020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121649</t>
+          <t>120411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27630</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23201</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48364</t>
+          <t>46947</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>38890</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68866</t>
+          <t>68740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1646642</t>
+          <t>1646619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1719448</t>
+          <t>1719172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1438642</t>
+          <t>1436356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1515428</t>
+          <t>1517478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3112331</t>
+          <t>3101073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3218821</t>
+          <t>3214362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>217648</t>
+          <t>219785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279583</t>
+          <t>281612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245806</t>
+          <t>246741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309570</t>
+          <t>307200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>482383</t>
+          <t>479104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>566371</t>
+          <t>568426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66436</t>
+          <t>66495</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102928</t>
+          <t>102607</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>140620</t>
+          <t>139982</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>190097</t>
+          <t>189417</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>215678</t>
+          <t>218613</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>279460</t>
+          <t>282386</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>19346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42959</t>
+          <t>43332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32128</t>
+          <t>31547</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59599</t>
+          <t>59575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55915</t>
+          <t>57824</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93968</t>
+          <t>93300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43495</t>
+          <t>42865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38742</t>
+          <t>37887</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41221</t>
+          <t>40141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72530</t>
+          <t>70865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>430475</t>
+          <t>428439</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>468469</t>
+          <t>469624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>423633</t>
+          <t>423109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>463013</t>
+          <t>462161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>868699</t>
+          <t>867385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>924402</t>
+          <t>922570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>48321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80305</t>
+          <t>79456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38618</t>
+          <t>39396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65764</t>
+          <t>69056</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95545</t>
+          <t>93636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139048</t>
+          <t>136802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>21877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44918</t>
+          <t>45231</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37827</t>
+          <t>37597</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66844</t>
+          <t>68032</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23376</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37320</t>
+          <t>35794</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13858</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>16450</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2590882</t>
+          <t>2598797</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2687556</t>
+          <t>2693695</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2398212</t>
+          <t>2401066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2513657</t>
+          <t>2509141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5025609</t>
+          <t>5024607</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5171193</t>
+          <t>5178217</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,01%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>380073</t>
+          <t>376680</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>457986</t>
+          <t>452377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>447164</t>
+          <t>450516</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>529044</t>
+          <t>530146</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>850780</t>
+          <t>843885</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>963362</t>
+          <t>962415</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174999</t>
+          <t>172915</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>229589</t>
+          <t>231443</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>347291</t>
+          <t>344445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425600</t>
+          <t>425879</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>538648</t>
+          <t>538032</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>633237</t>
+          <t>634376</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52889</t>
+          <t>53370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85811</t>
+          <t>86713</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106999</t>
+          <t>107498</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151760</t>
+          <t>154159</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171883</t>
+          <t>169614</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>228574</t>
+          <t>228958</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36910</t>
+          <t>36293</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65236</t>
+          <t>64873</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49727</t>
+          <t>50260</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>85514</t>
+          <t>84993</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92290</t>
+          <t>93994</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137391</t>
+          <t>137163</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>321216</t>
+          <t>371063</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>300338</t>
+          <t>348503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>341620</t>
+          <t>394749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>363315</t>
+          <t>398697</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>343714</t>
+          <t>376815</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>387795</t>
+          <t>419196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>684531</t>
+          <t>769761</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>655976</t>
+          <t>739577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>715479</t>
+          <t>801625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,41%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59701</t>
+          <t>65251</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47766</t>
+          <t>52159</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73741</t>
+          <t>78520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>107611</t>
+          <t>116835</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93837</t>
+          <t>101960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>131508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>167312</t>
+          <t>182086</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149228</t>
+          <t>164336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185722</t>
+          <t>204057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70333</t>
+          <t>75196</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84370</t>
+          <t>92246</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>148030</t>
+          <t>157132</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130708</t>
+          <t>141028</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168911</t>
+          <t>173297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>218363</t>
+          <t>232328</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>195171</t>
+          <t>209197</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>241429</t>
+          <t>254107</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39241</t>
+          <t>41377</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30012</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51100</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71896</t>
+          <t>78722</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60992</t>
+          <t>67336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84711</t>
+          <t>91336</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>111137</t>
+          <t>120098</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94183</t>
+          <t>103071</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127965</t>
+          <t>139282</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>24652</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>35101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61567</t>
+          <t>67338</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51486</t>
+          <t>57330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73218</t>
+          <t>80721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>85143</t>
+          <t>91991</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72102</t>
+          <t>78964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99822</t>
+          <t>106982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514067</t>
+          <t>577540</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514067</t>
+          <t>577540</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514067</t>
+          <t>577540</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>752419</t>
+          <t>818724</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>752419</t>
+          <t>818724</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>752419</t>
+          <t>818724</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1266486</t>
+          <t>1396264</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1266486</t>
+          <t>1396264</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1266486</t>
+          <t>1396264</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1877552</t>
+          <t>1777273</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1815456</t>
+          <t>1734958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1997995</t>
+          <t>1814097</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1522403</t>
+          <t>1603014</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1152756</t>
+          <t>1567225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1698362</t>
+          <t>1638671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3399955</t>
+          <t>3380287</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2874107</t>
+          <t>3325390</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3613054</t>
+          <t>3441675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>178605</t>
+          <t>191724</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124841</t>
+          <t>165500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214307</t>
+          <t>221315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>396542</t>
+          <t>210059</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>200629</t>
+          <t>188294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>830885</t>
+          <t>239060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>575147</t>
+          <t>401783</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>366808</t>
+          <t>366553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1189156</t>
+          <t>438566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>152459</t>
+          <t>168893</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106893</t>
+          <t>145796</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>184714</t>
+          <t>199023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>221205</t>
+          <t>248733</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164605</t>
+          <t>224601</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>261859</t>
+          <t>275808</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>373664</t>
+          <t>417626</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>296539</t>
+          <t>378625</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>425739</t>
+          <t>459193</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48377</t>
+          <t>54725</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33256</t>
+          <t>41022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65300</t>
+          <t>70503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62131</t>
+          <t>69915</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43998</t>
+          <t>57049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79345</t>
+          <t>84151</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>110508</t>
+          <t>124640</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89141</t>
+          <t>105670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134052</t>
+          <t>145683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31300</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>24150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44430</t>
+          <t>52743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34060</t>
+          <t>38082</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23763</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46868</t>
+          <t>50049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>65360</t>
+          <t>74018</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48176</t>
+          <t>58689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83688</t>
+          <t>93211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2288293</t>
+          <t>2228550</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2288293</t>
+          <t>2228550</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2288293</t>
+          <t>2228550</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2236342</t>
+          <t>2169803</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2236342</t>
+          <t>2169803</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2236342</t>
+          <t>2169803</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4524635</t>
+          <t>4398353</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4524635</t>
+          <t>4398353</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4524635</t>
+          <t>4398353</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>538208</t>
+          <t>591347</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>515261</t>
+          <t>568741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>556644</t>
+          <t>611033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>516201</t>
+          <t>572071</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>495997</t>
+          <t>551442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>532418</t>
+          <t>591839</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1054409</t>
+          <t>1163418</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1027058</t>
+          <t>1134192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1080035</t>
+          <t>1191486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40126</t>
+          <t>46664</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28845</t>
+          <t>34560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>64340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>68491</t>
+          <t>72620</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>59674</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83996</t>
+          <t>87695</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>108617</t>
+          <t>119284</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91493</t>
+          <t>101119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>128664</t>
+          <t>140445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43405</t>
+          <t>46680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31019</t>
+          <t>34416</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58178</t>
+          <t>63428</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>56524</t>
+          <t>67430</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45185</t>
+          <t>53564</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69634</t>
+          <t>81922</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>99929</t>
+          <t>114110</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>81451</t>
+          <t>93937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>121102</t>
+          <t>135069</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -11308,17 +11308,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20831</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29401</t>
+          <t>32787</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25449</t>
+          <t>26934</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,22 +11491,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>26358</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35461</t>
+          <t>37127</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2736976</t>
+          <t>2739684</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2662891</t>
+          <t>2684707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2904601</t>
+          <t>2789672</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2401919</t>
+          <t>2573782</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1958851</t>
+          <t>2527869</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2568323</t>
+          <t>2622996</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5138896</t>
+          <t>5313466</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4652273</t>
+          <t>5240645</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5352494</t>
+          <t>5386620</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>278433</t>
+          <t>303639</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216770</t>
+          <t>271160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>316653</t>
+          <t>338252</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>572645</t>
+          <t>399514</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>374026</t>
+          <t>368907</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1134743</t>
+          <t>430186</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>851077</t>
+          <t>703154</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>640042</t>
+          <t>655199</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1476292</t>
+          <t>748460</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>266197</t>
+          <t>290770</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202235</t>
+          <t>259971</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>304660</t>
+          <t>327442</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425759</t>
+          <t>473294</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>356255</t>
+          <t>439901</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>474055</t>
+          <t>513493</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>691956</t>
+          <t>764064</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>585932</t>
+          <t>716127</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>754070</t>
+          <t>817150</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>97478</t>
+          <t>106945</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73912</t>
+          <t>89038</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118778</t>
+          <t>129488</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>144998</t>
+          <t>161087</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118982</t>
+          <t>143226</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>166909</t>
+          <t>181107</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>242476</t>
+          <t>268032</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>208134</t>
+          <t>239171</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>276181</t>
+          <t>298630</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>76639</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51429</t>
+          <t>58631</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87678</t>
+          <t>95813</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>103903</t>
+          <t>115727</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82677</t>
+          <t>99410</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123093</t>
+          <t>132698</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>173803</t>
+          <t>192366</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>146929</t>
+          <t>169313</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>199889</t>
+          <t>217310</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3448984</t>
+          <t>3517677</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3448984</t>
+          <t>3517677</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3448984</t>
+          <t>3517677</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3649224</t>
+          <t>3723404</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3649224</t>
+          <t>3723404</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3649224</t>
+          <t>3723404</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7098208</t>
+          <t>7241082</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7098208</t>
+          <t>7241082</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7098208</t>
+          <t>7241082</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
